--- a/source/data/t1-readme-metadata-2026.xlsx
+++ b/source/data/t1-readme-metadata-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pxn045\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C4556E-CF16-4D7C-B030-3E18E8DE0BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363731DA-87CD-41BB-95BE-7F9FEDEC0172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3284,10 +3284,25 @@
   <dimension ref="A1:P123"/>
   <sheetFormatPr defaultColWidth="41.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="41.125" style="1"/>
+    <col min="1" max="1" width="41.125" style="1"/>
+    <col min="2" max="3" width="36" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="41.125" style="1"/>
+    <col min="8" max="8" width="31.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="41.125" style="1"/>
+    <col min="10" max="10" width="36" style="1" customWidth="1"/>
+    <col min="11" max="11" width="36.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="33.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="32.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="29.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="32.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="36.125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="41.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="30">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3338,7 +3353,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="71.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3356,7 +3371,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="5"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -3376,7 +3391,7 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" ht="71.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3388,7 +3403,7 @@
       <c r="D3" s="5"/>
       <c r="F3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -3402,7 +3417,7 @@
       <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="71.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3414,7 +3429,7 @@
       <c r="D4" s="5"/>
       <c r="F4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -3427,8 +3442,8 @@
       <c r="N4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="71.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:16" ht="99.75">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -3446,7 +3461,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -3465,8 +3480,8 @@
       </c>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" ht="71.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:16" ht="85.5">
+      <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -3504,7 +3519,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:16" ht="85.5">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -3516,7 +3531,7 @@
       <c r="D7" s="5"/>
       <c r="F7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -3530,7 +3545,7 @@
       <c r="P7" s="5"/>
     </row>
     <row r="8" spans="1:16" ht="71.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -3542,7 +3557,7 @@
       <c r="D8" s="5"/>
       <c r="F8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -3555,8 +3570,8 @@
       <c r="N8" s="5"/>
       <c r="P8" s="5"/>
     </row>
-    <row r="9" spans="1:16" ht="99.75">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:16" ht="128.25">
+      <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -3574,7 +3589,7 @@
         <v>69</v>
       </c>
       <c r="H9" s="5"/>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -3594,7 +3609,7 @@
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16" ht="71.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -3606,7 +3621,7 @@
       <c r="D10" s="5"/>
       <c r="F10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>57</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -3620,7 +3635,7 @@
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16" ht="71.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3632,7 +3647,7 @@
       <c r="D11" s="5"/>
       <c r="F11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>77</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -3646,7 +3661,7 @@
       <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16" ht="71.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -3658,7 +3673,7 @@
       <c r="D12" s="5"/>
       <c r="F12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -3672,7 +3687,7 @@
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16" ht="71.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -3690,7 +3705,7 @@
         <v>91</v>
       </c>
       <c r="H13" s="5"/>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -3710,7 +3725,7 @@
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16" ht="71.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -3728,7 +3743,7 @@
         <v>82</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -3748,7 +3763,7 @@
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16" ht="85.5">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>996</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -3760,7 +3775,7 @@
       <c r="D15" s="5"/>
       <c r="F15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="3" t="s">
         <v>999</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -3774,7 +3789,7 @@
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16" ht="71.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>992</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -3786,7 +3801,7 @@
       <c r="D16" s="5"/>
       <c r="F16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="3" t="s">
         <v>994</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -3799,8 +3814,8 @@
       <c r="N16" s="5"/>
       <c r="P16" s="5"/>
     </row>
-    <row r="17" spans="1:16" ht="71.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:16" ht="85.5">
+      <c r="A17" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -3818,7 +3833,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="3" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -3838,7 +3853,7 @@
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16" ht="71.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -3850,7 +3865,7 @@
       <c r="D18" s="5"/>
       <c r="F18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -3864,7 +3879,7 @@
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16" ht="71.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -3882,7 +3897,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -3902,7 +3917,7 @@
       <c r="P19" s="5"/>
     </row>
     <row r="20" spans="1:16" ht="71.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -3914,7 +3929,7 @@
       <c r="D20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -3928,7 +3943,7 @@
       <c r="P20" s="5"/>
     </row>
     <row r="21" spans="1:16" ht="71.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -3946,7 +3961,7 @@
         <v>128</v>
       </c>
       <c r="H21" s="5"/>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="3" t="s">
         <v>132</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -3966,7 +3981,7 @@
       <c r="P21" s="5"/>
     </row>
     <row r="22" spans="1:16" ht="71.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>135</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -3978,7 +3993,7 @@
       <c r="D22" s="5"/>
       <c r="F22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="3" t="s">
         <v>137</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -3992,7 +4007,7 @@
       <c r="P22" s="5"/>
     </row>
     <row r="23" spans="1:16" ht="71.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -4010,7 +4025,7 @@
         <v>142</v>
       </c>
       <c r="H23" s="5"/>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="3" t="s">
         <v>146</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -4030,7 +4045,7 @@
       <c r="P23" s="5"/>
     </row>
     <row r="24" spans="1:16" ht="71.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -4048,7 +4063,7 @@
         <v>151</v>
       </c>
       <c r="H24" s="5"/>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -4068,7 +4083,7 @@
       <c r="P24" s="5"/>
     </row>
     <row r="25" spans="1:16" ht="71.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>158</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -4086,7 +4101,7 @@
         <v>160</v>
       </c>
       <c r="H25" s="5"/>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -4105,8 +4120,8 @@
       </c>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:16" ht="71.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:16" ht="99.75">
+      <c r="A26" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -4124,7 +4139,7 @@
         <v>170</v>
       </c>
       <c r="H26" s="5"/>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="3" t="s">
         <v>174</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -4144,7 +4159,7 @@
       <c r="P26" s="5"/>
     </row>
     <row r="27" spans="1:16" ht="71.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>177</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -4162,7 +4177,7 @@
         <v>180</v>
       </c>
       <c r="H27" s="5"/>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="3" t="s">
         <v>184</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -4182,7 +4197,7 @@
       <c r="P27" s="5"/>
     </row>
     <row r="28" spans="1:16" ht="71.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -4200,7 +4215,7 @@
         <v>190</v>
       </c>
       <c r="H28" s="5"/>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="3" t="s">
         <v>194</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -4220,7 +4235,7 @@
       <c r="P28" s="5"/>
     </row>
     <row r="29" spans="1:16" ht="71.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -4238,7 +4253,7 @@
         <v>200</v>
       </c>
       <c r="H29" s="5"/>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="3" t="s">
         <v>204</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -4258,7 +4273,7 @@
       <c r="P29" s="5"/>
     </row>
     <row r="30" spans="1:16" ht="71.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -4270,7 +4285,7 @@
       <c r="D30" s="5"/>
       <c r="F30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="3" t="s">
         <v>209</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -4283,8 +4298,8 @@
       <c r="N30" s="5"/>
       <c r="P30" s="5"/>
     </row>
-    <row r="31" spans="1:16" ht="85.5">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:16" ht="114">
+      <c r="A31" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4302,7 +4317,7 @@
         <v>213</v>
       </c>
       <c r="H31" s="5"/>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="3" t="s">
         <v>217</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -4321,8 +4336,8 @@
       </c>
       <c r="P31" s="5"/>
     </row>
-    <row r="32" spans="1:16" ht="114">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:16" ht="128.25">
+      <c r="A32" s="3" t="s">
         <v>247</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -4340,7 +4355,7 @@
         <v>250</v>
       </c>
       <c r="H32" s="5"/>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="3" t="s">
         <v>254</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -4360,7 +4375,7 @@
       <c r="P32" s="5"/>
     </row>
     <row r="33" spans="1:16" ht="71.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -4372,7 +4387,7 @@
       <c r="D33" s="5"/>
       <c r="F33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="3" t="s">
         <v>221</v>
       </c>
       <c r="J33" s="1" t="s">
@@ -4385,8 +4400,8 @@
       <c r="N33" s="5"/>
       <c r="P33" s="5"/>
     </row>
-    <row r="34" spans="1:16" ht="99.75">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:16" ht="128.25">
+      <c r="A34" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -4404,7 +4419,7 @@
         <v>224</v>
       </c>
       <c r="H34" s="5"/>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="3" t="s">
         <v>227</v>
       </c>
       <c r="J34" s="1" t="s">
@@ -4423,8 +4438,8 @@
       </c>
       <c r="P34" s="5"/>
     </row>
-    <row r="35" spans="1:16" ht="85.5">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:16" ht="114">
+      <c r="A35" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -4442,7 +4457,7 @@
         <v>231</v>
       </c>
       <c r="H35" s="5"/>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="3" t="s">
         <v>235</v>
       </c>
       <c r="J35" s="1" t="s">
@@ -4462,7 +4477,7 @@
       <c r="P35" s="5"/>
     </row>
     <row r="36" spans="1:16" ht="71.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>237</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4480,7 +4495,7 @@
         <v>240</v>
       </c>
       <c r="H36" s="5"/>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="3" t="s">
         <v>244</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -4499,8 +4514,8 @@
       </c>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" ht="128.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:16" ht="156.75">
+      <c r="A37" s="3" t="s">
         <v>257</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -4518,7 +4533,7 @@
         <v>259</v>
       </c>
       <c r="H37" s="5"/>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="3" t="s">
         <v>263</v>
       </c>
       <c r="J37" s="1" t="s">
@@ -4537,8 +4552,8 @@
       </c>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" ht="114">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:16" ht="142.5">
+      <c r="A38" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -4556,7 +4571,7 @@
         <v>268</v>
       </c>
       <c r="H38" s="5"/>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="3" t="s">
         <v>272</v>
       </c>
       <c r="J38" s="1" t="s">
@@ -4576,7 +4591,7 @@
       <c r="P38" s="5"/>
     </row>
     <row r="39" spans="1:16" ht="71.25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>275</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -4594,7 +4609,7 @@
         <v>278</v>
       </c>
       <c r="H39" s="5"/>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="3" t="s">
         <v>282</v>
       </c>
       <c r="J39" s="1" t="s">
@@ -4613,8 +4628,8 @@
       </c>
       <c r="P39" s="5"/>
     </row>
-    <row r="40" spans="1:16" ht="114">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:16" ht="142.5">
+      <c r="A40" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -4632,7 +4647,7 @@
         <v>286</v>
       </c>
       <c r="H40" s="5"/>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="3" t="s">
         <v>289</v>
       </c>
       <c r="J40" s="1" t="s">
@@ -4651,8 +4666,8 @@
       </c>
       <c r="P40" s="5"/>
     </row>
-    <row r="41" spans="1:16" ht="71.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:16" ht="85.5">
+      <c r="A41" s="3" t="s">
         <v>307</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4670,7 +4685,7 @@
         <v>310</v>
       </c>
       <c r="H41" s="5"/>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="3" t="s">
         <v>314</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -4689,8 +4704,8 @@
       </c>
       <c r="P41" s="5"/>
     </row>
-    <row r="42" spans="1:16" ht="99.75">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:16" ht="114">
+      <c r="A42" s="3" t="s">
         <v>291</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -4708,7 +4723,7 @@
         <v>293</v>
       </c>
       <c r="H42" s="5"/>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="3" t="s">
         <v>297</v>
       </c>
       <c r="J42" s="1" t="s">
@@ -4728,7 +4743,7 @@
       <c r="P42" s="5"/>
     </row>
     <row r="43" spans="1:16" ht="71.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>316</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -4746,7 +4761,7 @@
         <v>318</v>
       </c>
       <c r="H43" s="5"/>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="3" t="s">
         <v>322</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -4765,8 +4780,8 @@
       </c>
       <c r="P43" s="5"/>
     </row>
-    <row r="44" spans="1:16" ht="114">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:16" ht="142.5">
+      <c r="A44" s="3" t="s">
         <v>299</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4784,7 +4799,7 @@
         <v>301</v>
       </c>
       <c r="H44" s="5"/>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="3" t="s">
         <v>305</v>
       </c>
       <c r="J44" s="1" t="s">
@@ -4803,8 +4818,8 @@
       </c>
       <c r="P44" s="5"/>
     </row>
-    <row r="45" spans="1:16" ht="114">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:16" ht="142.5">
+      <c r="A45" s="3" t="s">
         <v>324</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4822,7 +4837,7 @@
         <v>326</v>
       </c>
       <c r="H45" s="5"/>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="3" t="s">
         <v>330</v>
       </c>
       <c r="J45" s="1" t="s">
@@ -4841,8 +4856,8 @@
       </c>
       <c r="P45" s="5"/>
     </row>
-    <row r="46" spans="1:16" ht="185.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:16" ht="242.25">
+      <c r="A46" s="3" t="s">
         <v>332</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4860,7 +4875,7 @@
         <v>335</v>
       </c>
       <c r="H46" s="5"/>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="3" t="s">
         <v>339</v>
       </c>
       <c r="J46" s="1" t="s">
@@ -4879,8 +4894,8 @@
       </c>
       <c r="P46" s="5"/>
     </row>
-    <row r="47" spans="1:16" ht="99.75">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:16" ht="128.25">
+      <c r="A47" s="3" t="s">
         <v>366</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -4898,7 +4913,7 @@
         <v>369</v>
       </c>
       <c r="H47" s="5"/>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="3" t="s">
         <v>373</v>
       </c>
       <c r="J47" s="1" t="s">
@@ -4917,8 +4932,8 @@
       </c>
       <c r="P47" s="5"/>
     </row>
-    <row r="48" spans="1:16" ht="99.75">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:16" ht="128.25">
+      <c r="A48" s="3" t="s">
         <v>342</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4936,7 +4951,7 @@
         <v>344</v>
       </c>
       <c r="H48" s="5"/>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="3" t="s">
         <v>347</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -4955,8 +4970,8 @@
       </c>
       <c r="P48" s="5"/>
     </row>
-    <row r="49" spans="1:16" ht="85.5">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:16" ht="114">
+      <c r="A49" s="3" t="s">
         <v>350</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -4974,7 +4989,7 @@
         <v>352</v>
       </c>
       <c r="H49" s="5"/>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="3" t="s">
         <v>355</v>
       </c>
       <c r="J49" s="1" t="s">
@@ -4993,8 +5008,8 @@
       </c>
       <c r="P49" s="5"/>
     </row>
-    <row r="50" spans="1:16" ht="213.75">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:16" ht="285">
+      <c r="A50" s="3" t="s">
         <v>358</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -5012,7 +5027,7 @@
         <v>360</v>
       </c>
       <c r="H50" s="5"/>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="3" t="s">
         <v>364</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -5031,8 +5046,8 @@
       </c>
       <c r="P50" s="5"/>
     </row>
-    <row r="51" spans="1:16" ht="128.25">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:16" ht="171">
+      <c r="A51" s="3" t="s">
         <v>376</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -5050,7 +5065,7 @@
         <v>379</v>
       </c>
       <c r="H51" s="5"/>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="3" t="s">
         <v>383</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -5069,8 +5084,8 @@
       </c>
       <c r="P51" s="5"/>
     </row>
-    <row r="52" spans="1:16" ht="99.75">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:16" ht="128.25">
+      <c r="A52" s="3" t="s">
         <v>386</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -5088,7 +5103,7 @@
         <v>389</v>
       </c>
       <c r="H52" s="5"/>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="3" t="s">
         <v>393</v>
       </c>
       <c r="J52" s="1" t="s">
@@ -5107,8 +5122,8 @@
       </c>
       <c r="P52" s="5"/>
     </row>
-    <row r="53" spans="1:16" ht="99.75">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:16" ht="114">
+      <c r="A53" s="3" t="s">
         <v>396</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -5126,7 +5141,7 @@
         <v>399</v>
       </c>
       <c r="H53" s="5"/>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="3" t="s">
         <v>403</v>
       </c>
       <c r="J53" s="1" t="s">
@@ -5146,7 +5161,7 @@
       <c r="P53" s="5"/>
     </row>
     <row r="54" spans="1:16" ht="71.25">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="3" t="s">
         <v>406</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -5164,7 +5179,7 @@
         <v>409</v>
       </c>
       <c r="H54" s="5"/>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="3" t="s">
         <v>413</v>
       </c>
       <c r="J54" s="1" t="s">
@@ -5183,8 +5198,8 @@
       </c>
       <c r="P54" s="5"/>
     </row>
-    <row r="55" spans="1:16" ht="99.75">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:16" ht="128.25">
+      <c r="A55" s="3" t="s">
         <v>416</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -5202,7 +5217,7 @@
         <v>419</v>
       </c>
       <c r="H55" s="5"/>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="3" t="s">
         <v>423</v>
       </c>
       <c r="J55" s="1" t="s">
@@ -5221,8 +5236,8 @@
       </c>
       <c r="P55" s="5"/>
     </row>
-    <row r="56" spans="1:16" ht="128.25">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:16" ht="156.75">
+      <c r="A56" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -5240,7 +5255,7 @@
         <v>429</v>
       </c>
       <c r="H56" s="5"/>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="3" t="s">
         <v>433</v>
       </c>
       <c r="J56" s="1" t="s">
@@ -5259,8 +5274,8 @@
       </c>
       <c r="P56" s="5"/>
     </row>
-    <row r="57" spans="1:16" ht="99.75">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:16" ht="114">
+      <c r="A57" s="3" t="s">
         <v>452</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -5278,7 +5293,7 @@
         <v>455</v>
       </c>
       <c r="H57" s="5"/>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="3" t="s">
         <v>459</v>
       </c>
       <c r="J57" s="1" t="s">
@@ -5298,7 +5313,7 @@
       <c r="P57" s="5"/>
     </row>
     <row r="58" spans="1:16" ht="71.25">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="3" t="s">
         <v>462</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -5316,7 +5331,7 @@
         <v>465</v>
       </c>
       <c r="H58" s="5"/>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="3" t="s">
         <v>469</v>
       </c>
       <c r="J58" s="1" t="s">
@@ -5335,8 +5350,8 @@
       </c>
       <c r="P58" s="5"/>
     </row>
-    <row r="59" spans="1:16" ht="99.75">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:16" ht="114">
+      <c r="A59" s="3" t="s">
         <v>436</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -5354,7 +5369,7 @@
         <v>439</v>
       </c>
       <c r="H59" s="5"/>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="3" t="s">
         <v>443</v>
       </c>
       <c r="J59" s="1" t="s">
@@ -5373,8 +5388,8 @@
       </c>
       <c r="P59" s="5"/>
     </row>
-    <row r="60" spans="1:16" ht="85.5">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:16" ht="99.75">
+      <c r="A60" s="3" t="s">
         <v>472</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -5392,7 +5407,7 @@
         <v>475</v>
       </c>
       <c r="H60" s="5"/>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="3" t="s">
         <v>479</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -5412,7 +5427,7 @@
       <c r="P60" s="5"/>
     </row>
     <row r="61" spans="1:16" ht="71.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>446</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -5424,7 +5439,7 @@
       <c r="D61" s="5"/>
       <c r="F61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="3" t="s">
         <v>449</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -5437,8 +5452,8 @@
       <c r="N61" s="5"/>
       <c r="P61" s="5"/>
     </row>
-    <row r="62" spans="1:16" ht="85.5">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:16" ht="114">
+      <c r="A62" s="3" t="s">
         <v>508</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -5456,7 +5471,7 @@
         <v>511</v>
       </c>
       <c r="H62" s="5"/>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="3" t="s">
         <v>515</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -5476,7 +5491,7 @@
       <c r="P62" s="5"/>
     </row>
     <row r="63" spans="1:16" ht="71.25">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>518</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -5488,7 +5503,7 @@
       <c r="D63" s="5"/>
       <c r="F63" s="5"/>
       <c r="H63" s="5"/>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="3" t="s">
         <v>520</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -5502,7 +5517,7 @@
       <c r="P63" s="5"/>
     </row>
     <row r="64" spans="1:16" ht="71.25">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>482</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -5520,7 +5535,7 @@
         <v>484</v>
       </c>
       <c r="H64" s="5"/>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="3" t="s">
         <v>488</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -5540,7 +5555,7 @@
       <c r="P64" s="5"/>
     </row>
     <row r="65" spans="1:16" ht="71.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>532</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -5558,7 +5573,7 @@
         <v>534</v>
       </c>
       <c r="H65" s="5"/>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="3" t="s">
         <v>538</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -5578,7 +5593,7 @@
       <c r="P65" s="5"/>
     </row>
     <row r="66" spans="1:16" ht="71.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>522</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -5596,7 +5611,7 @@
         <v>525</v>
       </c>
       <c r="H66" s="5"/>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="3" t="s">
         <v>529</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -5615,8 +5630,8 @@
       </c>
       <c r="P66" s="5"/>
     </row>
-    <row r="67" spans="1:16" ht="71.25">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:16" ht="85.5">
+      <c r="A67" s="3" t="s">
         <v>490</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -5634,7 +5649,7 @@
         <v>493</v>
       </c>
       <c r="H67" s="5"/>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="3" t="s">
         <v>497</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -5653,8 +5668,8 @@
       </c>
       <c r="P67" s="5"/>
     </row>
-    <row r="68" spans="1:16" ht="71.25">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:16" ht="85.5">
+      <c r="A68" s="3" t="s">
         <v>500</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -5672,7 +5687,7 @@
         <v>502</v>
       </c>
       <c r="H68" s="5"/>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="3" t="s">
         <v>506</v>
       </c>
       <c r="J68" s="1" t="s">
@@ -5691,8 +5706,8 @@
       </c>
       <c r="P68" s="5"/>
     </row>
-    <row r="69" spans="1:16" ht="99.75">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:16" ht="114">
+      <c r="A69" s="3" t="s">
         <v>582</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -5710,7 +5725,7 @@
         <v>585</v>
       </c>
       <c r="H69" s="5"/>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="3" t="s">
         <v>589</v>
       </c>
       <c r="J69" s="1" t="s">
@@ -5729,8 +5744,8 @@
       </c>
       <c r="P69" s="5"/>
     </row>
-    <row r="70" spans="1:16" ht="128.25">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:16" ht="156.75">
+      <c r="A70" s="3" t="s">
         <v>540</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -5748,7 +5763,7 @@
         <v>543</v>
       </c>
       <c r="H70" s="5"/>
-      <c r="I70" s="1" t="s">
+      <c r="I70" s="3" t="s">
         <v>547</v>
       </c>
       <c r="J70" s="1" t="s">
@@ -5768,7 +5783,7 @@
       <c r="P70" s="5"/>
     </row>
     <row r="71" spans="1:16" ht="71.25">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>550</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -5786,7 +5801,7 @@
         <v>553</v>
       </c>
       <c r="H71" s="5"/>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="3" t="s">
         <v>557</v>
       </c>
       <c r="J71" s="1" t="s">
@@ -5805,8 +5820,8 @@
       </c>
       <c r="P71" s="5"/>
     </row>
-    <row r="72" spans="1:16" ht="114">
-      <c r="A72" s="1" t="s">
+    <row r="72" spans="1:16" ht="142.5">
+      <c r="A72" s="3" t="s">
         <v>560</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -5824,7 +5839,7 @@
         <v>561</v>
       </c>
       <c r="H72" s="5"/>
-      <c r="I72" s="1" t="s">
+      <c r="I72" s="3" t="s">
         <v>564</v>
       </c>
       <c r="J72" s="1" t="s">
@@ -5843,8 +5858,8 @@
       </c>
       <c r="P72" s="5"/>
     </row>
-    <row r="73" spans="1:16" ht="99.75">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:16" ht="114">
+      <c r="A73" s="3" t="s">
         <v>574</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -5862,7 +5877,7 @@
         <v>576</v>
       </c>
       <c r="H73" s="5"/>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="3" t="s">
         <v>580</v>
       </c>
       <c r="J73" s="1" t="s">
@@ -5882,7 +5897,7 @@
       <c r="P73" s="5"/>
     </row>
     <row r="74" spans="1:16" ht="71.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="3" t="s">
         <v>566</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -5900,7 +5915,7 @@
         <v>568</v>
       </c>
       <c r="H74" s="5"/>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="3" t="s">
         <v>572</v>
       </c>
       <c r="J74" s="1" t="s">
@@ -5919,8 +5934,8 @@
       </c>
       <c r="P74" s="5"/>
     </row>
-    <row r="75" spans="1:16" ht="128.25">
-      <c r="A75" s="1" t="s">
+    <row r="75" spans="1:16" ht="171">
+      <c r="A75" s="3" t="s">
         <v>616</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -5938,7 +5953,7 @@
         <v>619</v>
       </c>
       <c r="H75" s="5"/>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="3" t="s">
         <v>623</v>
       </c>
       <c r="J75" s="1" t="s">
@@ -5957,8 +5972,8 @@
       </c>
       <c r="P75" s="5"/>
     </row>
-    <row r="76" spans="1:16" ht="99.75">
-      <c r="A76" s="1" t="s">
+    <row r="76" spans="1:16" ht="128.25">
+      <c r="A76" s="3" t="s">
         <v>592</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -5995,8 +6010,8 @@
       </c>
       <c r="P76" s="5"/>
     </row>
-    <row r="77" spans="1:16" ht="85.5">
-      <c r="A77" s="1" t="s">
+    <row r="77" spans="1:16" ht="114">
+      <c r="A77" s="3" t="s">
         <v>602</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -6014,7 +6029,7 @@
         <v>605</v>
       </c>
       <c r="H77" s="5"/>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="3" t="s">
         <v>609</v>
       </c>
       <c r="J77" s="1" t="s">
@@ -6033,8 +6048,8 @@
       </c>
       <c r="P77" s="5"/>
     </row>
-    <row r="78" spans="1:16" ht="85.5">
-      <c r="A78" s="1" t="s">
+    <row r="78" spans="1:16" ht="99.75">
+      <c r="A78" s="3" t="s">
         <v>626</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -6052,7 +6067,7 @@
         <v>629</v>
       </c>
       <c r="H78" s="5"/>
-      <c r="I78" s="1" t="s">
+      <c r="I78" s="3" t="s">
         <v>633</v>
       </c>
       <c r="J78" s="1" t="s">
@@ -6072,7 +6087,7 @@
       <c r="P78" s="5"/>
     </row>
     <row r="79" spans="1:16" ht="71.25">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>612</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -6084,7 +6099,7 @@
       <c r="D79" s="5"/>
       <c r="F79" s="5"/>
       <c r="H79" s="5"/>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="3" t="s">
         <v>614</v>
       </c>
       <c r="J79" s="1" t="s">
@@ -6097,8 +6112,8 @@
       <c r="N79" s="5"/>
       <c r="P79" s="5"/>
     </row>
-    <row r="80" spans="1:16" ht="99.75">
-      <c r="A80" s="1" t="s">
+    <row r="80" spans="1:16" ht="128.25">
+      <c r="A80" s="3" t="s">
         <v>665</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -6116,7 +6131,7 @@
         <v>667</v>
       </c>
       <c r="H80" s="5"/>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="3" t="s">
         <v>671</v>
       </c>
       <c r="J80" s="1" t="s">
@@ -6135,8 +6150,8 @@
       </c>
       <c r="P80" s="5"/>
     </row>
-    <row r="81" spans="1:16" ht="99.75">
-      <c r="A81" s="1" t="s">
+    <row r="81" spans="1:16" ht="128.25">
+      <c r="A81" s="3" t="s">
         <v>636</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -6154,7 +6169,7 @@
         <v>639</v>
       </c>
       <c r="H81" s="5"/>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="3" t="s">
         <v>643</v>
       </c>
       <c r="J81" s="1" t="s">
@@ -6174,7 +6189,7 @@
       <c r="P81" s="5"/>
     </row>
     <row r="82" spans="1:16" ht="71.25">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="3" t="s">
         <v>646</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -6186,7 +6201,7 @@
       <c r="D82" s="5"/>
       <c r="F82" s="5"/>
       <c r="H82" s="5"/>
-      <c r="I82" s="1" t="s">
+      <c r="I82" s="3" t="s">
         <v>649</v>
       </c>
       <c r="J82" s="1" t="s">
@@ -6199,8 +6214,8 @@
       <c r="N82" s="5"/>
       <c r="P82" s="5"/>
     </row>
-    <row r="83" spans="1:16" ht="99.75">
-      <c r="A83" s="1" t="s">
+    <row r="83" spans="1:16" ht="128.25">
+      <c r="A83" s="3" t="s">
         <v>673</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -6218,7 +6233,7 @@
         <v>675</v>
       </c>
       <c r="H83" s="5"/>
-      <c r="I83" s="1" t="s">
+      <c r="I83" s="3" t="s">
         <v>679</v>
       </c>
       <c r="J83" s="1" t="s">
@@ -6237,8 +6252,8 @@
       </c>
       <c r="P83" s="5"/>
     </row>
-    <row r="84" spans="1:16" ht="99.75">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:16" ht="128.25">
+      <c r="A84" s="3" t="s">
         <v>651</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -6256,7 +6271,7 @@
         <v>652</v>
       </c>
       <c r="H84" s="5"/>
-      <c r="I84" s="1" t="s">
+      <c r="I84" s="3" t="s">
         <v>655</v>
       </c>
       <c r="J84" s="1" t="s">
@@ -6276,7 +6291,7 @@
       <c r="P84" s="5"/>
     </row>
     <row r="85" spans="1:16" ht="71.25">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="3" t="s">
         <v>681</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -6294,7 +6309,7 @@
         <v>683</v>
       </c>
       <c r="H85" s="5"/>
-      <c r="I85" s="1" t="s">
+      <c r="I85" s="3" t="s">
         <v>687</v>
       </c>
       <c r="J85" s="1" t="s">
@@ -6313,8 +6328,8 @@
       </c>
       <c r="P85" s="5"/>
     </row>
-    <row r="86" spans="1:16" ht="85.5">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:16" ht="114">
+      <c r="A86" s="3" t="s">
         <v>657</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -6332,7 +6347,7 @@
         <v>659</v>
       </c>
       <c r="H86" s="5"/>
-      <c r="I86" s="1" t="s">
+      <c r="I86" s="3" t="s">
         <v>663</v>
       </c>
       <c r="J86" s="1" t="s">
@@ -6351,8 +6366,8 @@
       </c>
       <c r="P86" s="5"/>
     </row>
-    <row r="87" spans="1:16" ht="114">
-      <c r="A87" s="1" t="s">
+    <row r="87" spans="1:16" ht="142.5">
+      <c r="A87" s="3" t="s">
         <v>689</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -6370,7 +6385,7 @@
         <v>692</v>
       </c>
       <c r="H87" s="5"/>
-      <c r="I87" s="1" t="s">
+      <c r="I87" s="3" t="s">
         <v>696</v>
       </c>
       <c r="J87" s="1" t="s">
@@ -6389,8 +6404,8 @@
       </c>
       <c r="P87" s="5"/>
     </row>
-    <row r="88" spans="1:16" ht="114">
-      <c r="A88" s="1" t="s">
+    <row r="88" spans="1:16" ht="156.75">
+      <c r="A88" s="3" t="s">
         <v>699</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -6408,7 +6423,7 @@
         <v>702</v>
       </c>
       <c r="H88" s="5"/>
-      <c r="I88" s="1" t="s">
+      <c r="I88" s="3" t="s">
         <v>706</v>
       </c>
       <c r="J88" s="1" t="s">
@@ -6427,8 +6442,8 @@
       </c>
       <c r="P88" s="5"/>
     </row>
-    <row r="89" spans="1:16" ht="114">
-      <c r="A89" s="1" t="s">
+    <row r="89" spans="1:16" ht="142.5">
+      <c r="A89" s="3" t="s">
         <v>709</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -6446,7 +6461,7 @@
         <v>692</v>
       </c>
       <c r="H89" s="5"/>
-      <c r="I89" s="1" t="s">
+      <c r="I89" s="3" t="s">
         <v>712</v>
       </c>
       <c r="J89" s="1" t="s">
@@ -6466,7 +6481,7 @@
       <c r="P89" s="5"/>
     </row>
     <row r="90" spans="1:16" ht="71.25">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="3" t="s">
         <v>715</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -6478,7 +6493,7 @@
       <c r="D90" s="5"/>
       <c r="F90" s="5"/>
       <c r="H90" s="5"/>
-      <c r="I90" s="1" t="s">
+      <c r="I90" s="3" t="s">
         <v>718</v>
       </c>
       <c r="J90" s="1" t="s">
@@ -6492,7 +6507,7 @@
       <c r="P90" s="5"/>
     </row>
     <row r="91" spans="1:16" ht="71.25">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="3" t="s">
         <v>721</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -6510,7 +6525,7 @@
         <v>724</v>
       </c>
       <c r="H91" s="5"/>
-      <c r="I91" s="1" t="s">
+      <c r="I91" s="3" t="s">
         <v>728</v>
       </c>
       <c r="J91" s="1" t="s">
@@ -6529,8 +6544,8 @@
       </c>
       <c r="P91" s="5"/>
     </row>
-    <row r="92" spans="1:16" ht="99.75">
-      <c r="A92" s="1" t="s">
+    <row r="92" spans="1:16" ht="114">
+      <c r="A92" s="3" t="s">
         <v>755</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -6548,7 +6563,7 @@
         <v>758</v>
       </c>
       <c r="H92" s="5"/>
-      <c r="I92" s="1" t="s">
+      <c r="I92" s="3" t="s">
         <v>762</v>
       </c>
       <c r="J92" s="1" t="s">
@@ -6568,7 +6583,7 @@
       <c r="P92" s="5"/>
     </row>
     <row r="93" spans="1:16" ht="71.25">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="3" t="s">
         <v>765</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -6580,7 +6595,7 @@
       <c r="D93" s="5"/>
       <c r="F93" s="5"/>
       <c r="H93" s="5"/>
-      <c r="I93" s="1" t="s">
+      <c r="I93" s="3" t="s">
         <v>767</v>
       </c>
       <c r="J93" s="1" t="s">
@@ -6593,8 +6608,8 @@
       <c r="N93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" ht="85.5">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:16" ht="99.75">
+      <c r="A94" s="3" t="s">
         <v>770</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -6612,7 +6627,7 @@
         <v>773</v>
       </c>
       <c r="H94" s="5"/>
-      <c r="I94" s="1" t="s">
+      <c r="I94" s="3" t="s">
         <v>777</v>
       </c>
       <c r="J94" s="1" t="s">
@@ -6631,8 +6646,8 @@
       </c>
       <c r="P94" s="5"/>
     </row>
-    <row r="95" spans="1:16" ht="114">
-      <c r="A95" s="1" t="s">
+    <row r="95" spans="1:16" ht="156.75">
+      <c r="A95" s="3" t="s">
         <v>731</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -6650,7 +6665,7 @@
         <v>733</v>
       </c>
       <c r="H95" s="5"/>
-      <c r="I95" s="1" t="s">
+      <c r="I95" s="3" t="s">
         <v>737</v>
       </c>
       <c r="J95" s="1" t="s">
@@ -6669,8 +6684,8 @@
       </c>
       <c r="P95" s="5"/>
     </row>
-    <row r="96" spans="1:16" ht="114">
-      <c r="A96" s="1" t="s">
+    <row r="96" spans="1:16" ht="142.5">
+      <c r="A96" s="3" t="s">
         <v>739</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -6688,7 +6703,7 @@
         <v>692</v>
       </c>
       <c r="H96" s="5"/>
-      <c r="I96" s="1" t="s">
+      <c r="I96" s="3" t="s">
         <v>742</v>
       </c>
       <c r="J96" s="1" t="s">
@@ -6707,8 +6722,8 @@
       </c>
       <c r="P96" s="5"/>
     </row>
-    <row r="97" spans="1:16" ht="142.5">
-      <c r="A97" s="1" t="s">
+    <row r="97" spans="1:16" ht="171">
+      <c r="A97" s="3" t="s">
         <v>745</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -6726,7 +6741,7 @@
         <v>748</v>
       </c>
       <c r="H97" s="5"/>
-      <c r="I97" s="1" t="s">
+      <c r="I97" s="3" t="s">
         <v>752</v>
       </c>
       <c r="J97" s="1" t="s">
@@ -6745,8 +6760,8 @@
       </c>
       <c r="P97" s="5"/>
     </row>
-    <row r="98" spans="1:16" ht="114">
-      <c r="A98" s="1" t="s">
+    <row r="98" spans="1:16" ht="142.5">
+      <c r="A98" s="3" t="s">
         <v>952</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -6764,7 +6779,7 @@
         <v>955</v>
       </c>
       <c r="H98" s="5"/>
-      <c r="I98" s="1" t="s">
+      <c r="I98" s="3" t="s">
         <v>959</v>
       </c>
       <c r="J98" s="1" t="s">
@@ -6783,8 +6798,8 @@
       </c>
       <c r="P98" s="5"/>
     </row>
-    <row r="99" spans="1:16" ht="128.25">
-      <c r="A99" s="1" t="s">
+    <row r="99" spans="1:16" ht="156.75">
+      <c r="A99" s="3" t="s">
         <v>962</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -6802,7 +6817,7 @@
         <v>965</v>
       </c>
       <c r="H99" s="5"/>
-      <c r="I99" s="1" t="s">
+      <c r="I99" s="3" t="s">
         <v>969</v>
       </c>
       <c r="J99" s="1" t="s">
@@ -6821,8 +6836,8 @@
       </c>
       <c r="P99" s="5"/>
     </row>
-    <row r="100" spans="1:16" ht="99.75">
-      <c r="A100" s="1" t="s">
+    <row r="100" spans="1:16" ht="128.25">
+      <c r="A100" s="3" t="s">
         <v>972</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -6840,7 +6855,7 @@
         <v>975</v>
       </c>
       <c r="H100" s="5"/>
-      <c r="I100" s="1" t="s">
+      <c r="I100" s="3" t="s">
         <v>979</v>
       </c>
       <c r="J100" s="1" t="s">
@@ -6859,8 +6874,8 @@
       </c>
       <c r="P100" s="5"/>
     </row>
-    <row r="101" spans="1:16" ht="85.5">
-      <c r="A101" s="1" t="s">
+    <row r="101" spans="1:16" ht="114">
+      <c r="A101" s="3" t="s">
         <v>982</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -6878,7 +6893,7 @@
         <v>985</v>
       </c>
       <c r="H101" s="5"/>
-      <c r="I101" s="1" t="s">
+      <c r="I101" s="3" t="s">
         <v>989</v>
       </c>
       <c r="J101" s="1" t="s">
@@ -6898,7 +6913,7 @@
       <c r="P101" s="5"/>
     </row>
     <row r="102" spans="1:16" ht="71.25">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="3" t="s">
         <v>847</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -6910,7 +6925,7 @@
       <c r="D102" s="5"/>
       <c r="F102" s="5"/>
       <c r="H102" s="5"/>
-      <c r="I102" s="1" t="s">
+      <c r="I102" s="3" t="s">
         <v>849</v>
       </c>
       <c r="J102" s="1" t="s">
@@ -6924,7 +6939,7 @@
       <c r="P102" s="5"/>
     </row>
     <row r="103" spans="1:16" ht="71.25">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="3" t="s">
         <v>780</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -6942,7 +6957,7 @@
         <v>783</v>
       </c>
       <c r="H103" s="5"/>
-      <c r="I103" s="1" t="s">
+      <c r="I103" s="3" t="s">
         <v>787</v>
       </c>
       <c r="J103" s="1" t="s">
@@ -6962,7 +6977,7 @@
       <c r="P103" s="5"/>
     </row>
     <row r="104" spans="1:16" ht="71.25">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="3" t="s">
         <v>829</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -6980,7 +6995,7 @@
         <v>831</v>
       </c>
       <c r="H104" s="5"/>
-      <c r="I104" s="1" t="s">
+      <c r="I104" s="3" t="s">
         <v>835</v>
       </c>
       <c r="J104" s="1" t="s">
@@ -6999,8 +7014,8 @@
       </c>
       <c r="P104" s="5"/>
     </row>
-    <row r="105" spans="1:16" ht="71.25">
-      <c r="A105" s="1" t="s">
+    <row r="105" spans="1:16" ht="85.5">
+      <c r="A105" s="3" t="s">
         <v>790</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -7018,7 +7033,7 @@
         <v>792</v>
       </c>
       <c r="H105" s="5"/>
-      <c r="I105" s="1" t="s">
+      <c r="I105" s="3" t="s">
         <v>796</v>
       </c>
       <c r="J105" s="1" t="s">
@@ -7037,8 +7052,8 @@
       </c>
       <c r="P105" s="5"/>
     </row>
-    <row r="106" spans="1:16" ht="71.25">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="1:16" ht="99.75">
+      <c r="A106" s="3" t="s">
         <v>799</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -7056,7 +7071,7 @@
         <v>802</v>
       </c>
       <c r="H106" s="5"/>
-      <c r="I106" s="1" t="s">
+      <c r="I106" s="3" t="s">
         <v>806</v>
       </c>
       <c r="J106" s="1" t="s">
@@ -7076,7 +7091,7 @@
       <c r="P106" s="5"/>
     </row>
     <row r="107" spans="1:16" ht="71.25">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="3" t="s">
         <v>809</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -7094,7 +7109,7 @@
         <v>812</v>
       </c>
       <c r="H107" s="5"/>
-      <c r="I107" s="1" t="s">
+      <c r="I107" s="3" t="s">
         <v>816</v>
       </c>
       <c r="J107" s="1" t="s">
@@ -7114,7 +7129,7 @@
       <c r="P107" s="5"/>
     </row>
     <row r="108" spans="1:16" ht="71.25">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="3" t="s">
         <v>837</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -7132,7 +7147,7 @@
         <v>840</v>
       </c>
       <c r="H108" s="5"/>
-      <c r="I108" s="1" t="s">
+      <c r="I108" s="3" t="s">
         <v>844</v>
       </c>
       <c r="J108" s="1" t="s">
@@ -7152,7 +7167,7 @@
       <c r="P108" s="5"/>
     </row>
     <row r="109" spans="1:16" ht="71.25">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="3" t="s">
         <v>819</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -7170,7 +7185,7 @@
         <v>822</v>
       </c>
       <c r="H109" s="5"/>
-      <c r="I109" s="1" t="s">
+      <c r="I109" s="3" t="s">
         <v>826</v>
       </c>
       <c r="J109" s="1" t="s">
@@ -7189,8 +7204,8 @@
       </c>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" ht="199.5">
-      <c r="A110" s="1" t="s">
+    <row r="110" spans="1:16" ht="256.5">
+      <c r="A110" s="3" t="s">
         <v>851</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -7208,7 +7223,7 @@
         <v>853</v>
       </c>
       <c r="H110" s="5"/>
-      <c r="I110" s="1" t="s">
+      <c r="I110" s="3" t="s">
         <v>857</v>
       </c>
       <c r="J110" s="1" t="s">
@@ -7227,8 +7242,8 @@
       </c>
       <c r="P110" s="5"/>
     </row>
-    <row r="111" spans="1:16" ht="114">
-      <c r="A111" s="1" t="s">
+    <row r="111" spans="1:16" ht="128.25">
+      <c r="A111" s="3" t="s">
         <v>881</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -7246,7 +7261,7 @@
         <v>883</v>
       </c>
       <c r="H111" s="5"/>
-      <c r="I111" s="1" t="s">
+      <c r="I111" s="3" t="s">
         <v>887</v>
       </c>
       <c r="J111" s="1" t="s">
@@ -7265,8 +7280,8 @@
       </c>
       <c r="P111" s="5"/>
     </row>
-    <row r="112" spans="1:16" ht="99.75">
-      <c r="A112" s="1" t="s">
+    <row r="112" spans="1:16" ht="128.25">
+      <c r="A112" s="3" t="s">
         <v>859</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -7284,7 +7299,7 @@
         <v>860</v>
       </c>
       <c r="H112" s="5"/>
-      <c r="I112" s="1" t="s">
+      <c r="I112" s="3" t="s">
         <v>863</v>
       </c>
       <c r="J112" s="1" t="s">
@@ -7304,7 +7319,7 @@
       <c r="P112" s="5"/>
     </row>
     <row r="113" spans="1:16" ht="71.25">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="3" t="s">
         <v>865</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -7316,7 +7331,7 @@
       <c r="D113" s="5"/>
       <c r="F113" s="5"/>
       <c r="H113" s="5"/>
-      <c r="I113" s="1" t="s">
+      <c r="I113" s="3" t="s">
         <v>867</v>
       </c>
       <c r="J113" s="1" t="s">
@@ -7329,8 +7344,8 @@
       <c r="N113" s="5"/>
       <c r="P113" s="5"/>
     </row>
-    <row r="114" spans="1:16" ht="114">
-      <c r="A114" s="1" t="s">
+    <row r="114" spans="1:16" ht="128.25">
+      <c r="A114" s="3" t="s">
         <v>869</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -7348,7 +7363,7 @@
         <v>871</v>
       </c>
       <c r="H114" s="5"/>
-      <c r="I114" s="1" t="s">
+      <c r="I114" s="3" t="s">
         <v>875</v>
       </c>
       <c r="J114" s="1" t="s">
@@ -7368,7 +7383,7 @@
       <c r="P114" s="5"/>
     </row>
     <row r="115" spans="1:16" ht="71.25">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="3" t="s">
         <v>877</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -7380,7 +7395,7 @@
       <c r="D115" s="5"/>
       <c r="F115" s="5"/>
       <c r="H115" s="5"/>
-      <c r="I115" s="1" t="s">
+      <c r="I115" s="3" t="s">
         <v>879</v>
       </c>
       <c r="J115" s="1" t="s">
@@ -7393,8 +7408,8 @@
       <c r="N115" s="5"/>
       <c r="P115" s="5"/>
     </row>
-    <row r="116" spans="1:16" ht="142.5">
-      <c r="A116" s="1" t="s">
+    <row r="116" spans="1:16" ht="185.25">
+      <c r="A116" s="3" t="s">
         <v>890</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -7412,7 +7427,7 @@
         <v>892</v>
       </c>
       <c r="H116" s="5"/>
-      <c r="I116" s="1" t="s">
+      <c r="I116" s="3" t="s">
         <v>896</v>
       </c>
       <c r="J116" s="1" t="s">
@@ -7431,8 +7446,8 @@
       </c>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" ht="85.5">
-      <c r="A117" s="1" t="s">
+    <row r="117" spans="1:16" ht="114">
+      <c r="A117" s="3" t="s">
         <v>921</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -7450,7 +7465,7 @@
         <v>923</v>
       </c>
       <c r="H117" s="5"/>
-      <c r="I117" s="1" t="s">
+      <c r="I117" s="3" t="s">
         <v>927</v>
       </c>
       <c r="J117" s="1" t="s">
@@ -7469,8 +7484,8 @@
       </c>
       <c r="P117" s="5"/>
     </row>
-    <row r="118" spans="1:16" ht="99.75">
-      <c r="A118" s="1" t="s">
+    <row r="118" spans="1:16" ht="128.25">
+      <c r="A118" s="3" t="s">
         <v>898</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -7488,7 +7503,7 @@
         <v>900</v>
       </c>
       <c r="H118" s="5"/>
-      <c r="I118" s="1" t="s">
+      <c r="I118" s="3" t="s">
         <v>904</v>
       </c>
       <c r="J118" s="1" t="s">
@@ -7508,7 +7523,7 @@
       <c r="P118" s="5"/>
     </row>
     <row r="119" spans="1:16" ht="71.25">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="3" t="s">
         <v>907</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -7526,7 +7541,7 @@
         <v>910</v>
       </c>
       <c r="H119" s="5"/>
-      <c r="I119" s="1" t="s">
+      <c r="I119" s="3" t="s">
         <v>914</v>
       </c>
       <c r="J119" s="1" t="s">
@@ -7545,8 +7560,8 @@
       </c>
       <c r="P119" s="5"/>
     </row>
-    <row r="120" spans="1:16" ht="99.75">
-      <c r="A120" s="1" t="s">
+    <row r="120" spans="1:16" ht="128.25">
+      <c r="A120" s="3" t="s">
         <v>930</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -7564,7 +7579,7 @@
         <v>932</v>
       </c>
       <c r="H120" s="5"/>
-      <c r="I120" s="1" t="s">
+      <c r="I120" s="3" t="s">
         <v>936</v>
       </c>
       <c r="J120" s="1" t="s">
@@ -7584,7 +7599,7 @@
       <c r="P120" s="5"/>
     </row>
     <row r="121" spans="1:16" ht="71.25">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="3" t="s">
         <v>917</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -7596,7 +7611,7 @@
       <c r="D121" s="5"/>
       <c r="F121" s="5"/>
       <c r="H121" s="5"/>
-      <c r="I121" s="1" t="s">
+      <c r="I121" s="3" t="s">
         <v>919</v>
       </c>
       <c r="J121" s="1" t="s">
@@ -7609,8 +7624,8 @@
       <c r="N121" s="5"/>
       <c r="P121" s="5"/>
     </row>
-    <row r="122" spans="1:16" ht="99.75">
-      <c r="A122" s="1" t="s">
+    <row r="122" spans="1:16" ht="128.25">
+      <c r="A122" s="3" t="s">
         <v>938</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -7628,7 +7643,7 @@
         <v>939</v>
       </c>
       <c r="H122" s="5"/>
-      <c r="I122" s="1" t="s">
+      <c r="I122" s="3" t="s">
         <v>942</v>
       </c>
       <c r="J122" s="1" t="s">
@@ -7647,8 +7662,8 @@
       </c>
       <c r="P122" s="5"/>
     </row>
-    <row r="123" spans="1:16" ht="114">
-      <c r="A123" s="1" t="s">
+    <row r="123" spans="1:16" ht="156.75">
+      <c r="A123" s="3" t="s">
         <v>944</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -7666,7 +7681,7 @@
         <v>946</v>
       </c>
       <c r="H123" s="5"/>
-      <c r="I123" s="1" t="s">
+      <c r="I123" s="3" t="s">
         <v>950</v>
       </c>
       <c r="J123" s="1" t="s">
@@ -7693,6 +7708,248 @@
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="I6" r:id="rId1" xr:uid="{0B91E503-97E3-4504-BC3C-08694E1D3E69}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{D2CBC56E-C725-4F62-A112-45921C52FEEE}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{E9625F93-384D-4F6E-A890-A1A713295BA5}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{72DAC4F5-353D-4D30-B0E0-0745DA5B4780}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{975B8FD1-7C1C-4FB7-9F12-7DA9478EBD69}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{A160867A-E978-47BB-8340-2825846210B8}"/>
+    <hyperlink ref="A7" r:id="rId7" xr:uid="{1D1CE66C-09A3-4C91-ADF4-63DB602E07E8}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{D9EA4D2B-FA29-4F8B-AA97-8930BE3A7B0C}"/>
+    <hyperlink ref="A9" r:id="rId9" xr:uid="{46CF0F80-5FD7-4A3F-8096-B060303D0CD5}"/>
+    <hyperlink ref="A10" r:id="rId10" xr:uid="{52A79397-0EE6-47A0-848C-6D4E6A8B58A1}"/>
+    <hyperlink ref="A11" r:id="rId11" xr:uid="{F6D72FA0-9D8E-4C61-B160-E71B18FF3C86}"/>
+    <hyperlink ref="A12" r:id="rId12" xr:uid="{C5C26497-9D01-4166-8D71-47CFE5440BB2}"/>
+    <hyperlink ref="A13" r:id="rId13" xr:uid="{5088D9C5-F565-44E7-8BA7-C4860660274B}"/>
+    <hyperlink ref="A14" r:id="rId14" xr:uid="{BEC5D9B8-BC4B-452A-9591-299E467298EE}"/>
+    <hyperlink ref="A15" r:id="rId15" xr:uid="{2EC1664A-98FA-44B8-98BF-8278A3FCB613}"/>
+    <hyperlink ref="A16" r:id="rId16" xr:uid="{07CF1D39-3740-4B59-BA71-DFE4F6E55538}"/>
+    <hyperlink ref="A17" r:id="rId17" xr:uid="{0DA4462F-E97B-4EA5-8BDE-58362847790F}"/>
+    <hyperlink ref="A18" r:id="rId18" xr:uid="{B33D828B-578C-4C7F-9723-185C125A1CE3}"/>
+    <hyperlink ref="A19" r:id="rId19" xr:uid="{92AEEF72-111E-4003-B900-FD8D9532AF8D}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{C7F209D8-FCBE-43B3-953C-07CC85D7119A}"/>
+    <hyperlink ref="A21" r:id="rId21" xr:uid="{43FB1668-3BBC-466F-A623-85AD9DE624E6}"/>
+    <hyperlink ref="A22" r:id="rId22" xr:uid="{9D5FE0B7-CE39-4823-9230-B6F5CFCFB988}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{C80D5690-0105-4A06-ADA4-6F3C6DD5606C}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{8EA9A51B-2761-4AE5-8BF2-E7E0E0897B5A}"/>
+    <hyperlink ref="A23" r:id="rId25" xr:uid="{D6978D3A-E42E-436A-BE49-BA2BF5A28E54}"/>
+    <hyperlink ref="A26" r:id="rId26" xr:uid="{A0A1E0FB-50BB-4C27-8EF0-EACE6C0BBA41}"/>
+    <hyperlink ref="A27" r:id="rId27" xr:uid="{A81B1CE3-A6F4-4DA9-9809-70A94DAFAEEB}"/>
+    <hyperlink ref="A28" r:id="rId28" xr:uid="{84849C4E-9719-486B-A0AD-DDEC0BF127D5}"/>
+    <hyperlink ref="A29" r:id="rId29" xr:uid="{24FB97BC-0D3B-4486-90E9-F24A8840A7A9}"/>
+    <hyperlink ref="A30" r:id="rId30" xr:uid="{EE19BB2D-0405-45A3-907D-B4C160D35511}"/>
+    <hyperlink ref="A31" r:id="rId31" xr:uid="{768483EC-8FD7-4787-B08A-3E62F61E2C7F}"/>
+    <hyperlink ref="A32" r:id="rId32" xr:uid="{8E7D8DC5-65F8-4943-992B-AFA8E79DA97C}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{204DDD54-B386-4F90-B6A2-63E787A91EC5}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{5EB8134D-41E9-4D40-8AE9-FFB849A8B5A4}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{179D92B0-1259-43CD-8570-F595A409C1A3}"/>
+    <hyperlink ref="A38" r:id="rId36" xr:uid="{34A92236-40B5-463D-8936-A11C0E57A276}"/>
+    <hyperlink ref="A39" r:id="rId37" xr:uid="{9B9779CE-02BC-4C37-AD51-723C78922A43}"/>
+    <hyperlink ref="A41" r:id="rId38" xr:uid="{25365F0F-F375-46E6-8299-5F7CF2D3EA9E}"/>
+    <hyperlink ref="A43" r:id="rId39" xr:uid="{CA5D4894-BA9A-47BB-92EF-9D69AE8DBCC2}"/>
+    <hyperlink ref="A45" r:id="rId40" xr:uid="{5FF9C9FD-A4A6-49DC-A0BD-B14DC937CC22}"/>
+    <hyperlink ref="A47" r:id="rId41" xr:uid="{22A9C1C6-0181-440A-A76F-1B75547C8995}"/>
+    <hyperlink ref="A49" r:id="rId42" xr:uid="{DD750D41-A5CC-4626-86F5-0F49D8E19A3C}"/>
+    <hyperlink ref="A50" r:id="rId43" xr:uid="{18CC8B3C-33B0-43CB-8864-BC21B9B31836}"/>
+    <hyperlink ref="A51" r:id="rId44" xr:uid="{5BE836C8-CFBF-47DE-8D7A-F765D8A26060}"/>
+    <hyperlink ref="A53" r:id="rId45" xr:uid="{CB59C137-0D40-43EF-B584-B66EA0315A6B}"/>
+    <hyperlink ref="A55" r:id="rId46" xr:uid="{25E169A9-F4A7-4255-BDCA-B1631F21A2D0}"/>
+    <hyperlink ref="A57" r:id="rId47" xr:uid="{572E0536-4086-4B68-9A40-64416B9A3384}"/>
+    <hyperlink ref="A59" r:id="rId48" xr:uid="{DDB824ED-3A72-4117-8AA5-F46CDF21915B}"/>
+    <hyperlink ref="A61" r:id="rId49" xr:uid="{26A489A9-9ED6-4055-B34E-230400EB9300}"/>
+    <hyperlink ref="A63" r:id="rId50" xr:uid="{C24275C1-3F7E-42D7-96EF-95D49DEC8C99}"/>
+    <hyperlink ref="A65" r:id="rId51" xr:uid="{5ACBA516-6304-4739-959E-91751BA9033C}"/>
+    <hyperlink ref="A66" r:id="rId52" xr:uid="{3E2AEB40-2633-443A-9E42-2CFA2927A7FF}"/>
+    <hyperlink ref="A67" r:id="rId53" xr:uid="{CE30B6F4-81CE-495E-8962-EB239907CDE1}"/>
+    <hyperlink ref="A68" r:id="rId54" xr:uid="{37C9E711-AAAA-4467-8D56-3941B5116C60}"/>
+    <hyperlink ref="A33" r:id="rId55" xr:uid="{6EE665F6-E8A9-4106-915F-E86FD5091E57}"/>
+    <hyperlink ref="A37" r:id="rId56" xr:uid="{BF2FACDA-28F6-4BFC-8E22-C762AF0EBA01}"/>
+    <hyperlink ref="A40" r:id="rId57" xr:uid="{DD401951-90F4-48D9-A6D3-74EF4089B1FC}"/>
+    <hyperlink ref="A42" r:id="rId58" xr:uid="{2D356B7D-7A5B-4963-BF34-F75DF5C91349}"/>
+    <hyperlink ref="A44" r:id="rId59" xr:uid="{1D059F45-6F9D-4027-A0A3-A4D5E9FF3F61}"/>
+    <hyperlink ref="A46" r:id="rId60" xr:uid="{FF33E232-D9E5-4D2C-AED0-351B600E3ECA}"/>
+    <hyperlink ref="A48" r:id="rId61" xr:uid="{5DBDC014-8D3D-4AE5-84AF-FE85C18C5807}"/>
+    <hyperlink ref="A52" r:id="rId62" xr:uid="{9EC37E31-1BF2-43DE-B86F-5494FBBB5F81}"/>
+    <hyperlink ref="A54" r:id="rId63" xr:uid="{5AE1B474-7A8F-4B99-94E1-F620DDAAA29F}"/>
+    <hyperlink ref="A56" r:id="rId64" xr:uid="{3A2FE014-A122-4A84-9149-3754C2C086D1}"/>
+    <hyperlink ref="A58" r:id="rId65" xr:uid="{EB57B396-4D39-4637-B19E-4E60E3FC6439}"/>
+    <hyperlink ref="A60" r:id="rId66" xr:uid="{FF501043-FC32-440B-BE5B-D6DEB84CA395}"/>
+    <hyperlink ref="A62" r:id="rId67" xr:uid="{AE73FAD2-DF6F-4EB4-838C-D822C1EE63DB}"/>
+    <hyperlink ref="A64" r:id="rId68" xr:uid="{3007810C-A4E3-4AD1-9D61-29AF4B288C03}"/>
+    <hyperlink ref="A69" r:id="rId69" xr:uid="{DA10ADCC-1478-44A4-B56D-B13A5D0A0B0A}"/>
+    <hyperlink ref="A70" r:id="rId70" xr:uid="{C97C08DD-1C0A-48E5-943F-B6F200E7A034}"/>
+    <hyperlink ref="A71" r:id="rId71" xr:uid="{5F0C5482-8014-407B-82A7-2393A2F7745E}"/>
+    <hyperlink ref="A72" r:id="rId72" xr:uid="{EBCB11ED-D74A-4433-9DDA-4159163A5FC2}"/>
+    <hyperlink ref="A73" r:id="rId73" xr:uid="{1F7E06B2-16A3-4F4F-9E3B-4D3CAEFF5249}"/>
+    <hyperlink ref="A74" r:id="rId74" xr:uid="{40430B31-5D04-45F9-923D-19E261DCD7A2}"/>
+    <hyperlink ref="A75" r:id="rId75" xr:uid="{4BDDFCD2-FDA1-4B0B-80FC-4F5FD9A3F8A7}"/>
+    <hyperlink ref="A76" r:id="rId76" xr:uid="{A57FDA38-5A97-4CEE-B035-76567166344A}"/>
+    <hyperlink ref="A77" r:id="rId77" xr:uid="{14CDA4EA-54D4-432D-9DF8-14E15EF1025E}"/>
+    <hyperlink ref="A78" r:id="rId78" xr:uid="{BD3C44C8-E94F-491A-8FAD-BBC6905C4B10}"/>
+    <hyperlink ref="A79" r:id="rId79" xr:uid="{E7546411-AB99-44A4-9964-454F375A99B2}"/>
+    <hyperlink ref="A80" r:id="rId80" xr:uid="{AD02F072-8AEF-4E27-B0E0-3F118D1FC3BE}"/>
+    <hyperlink ref="A82" r:id="rId81" xr:uid="{5759B7E0-77C4-4AFD-BD09-1889BBF5AB6C}"/>
+    <hyperlink ref="A83" r:id="rId82" xr:uid="{F82D7C24-C0B8-46C8-ABC1-A6A7A12EB4E6}"/>
+    <hyperlink ref="A84" r:id="rId83" xr:uid="{A5A156D0-9EDA-4A0D-837E-A27606F13695}"/>
+    <hyperlink ref="A86" r:id="rId84" xr:uid="{3EFD139D-C8C7-4D87-9C03-600B03A6A358}"/>
+    <hyperlink ref="A88" r:id="rId85" xr:uid="{C1B04E7A-75F3-41DB-9A5D-26F930F851E5}"/>
+    <hyperlink ref="A89" r:id="rId86" xr:uid="{E4C2A852-93CF-4063-BBC5-B9258A6E8919}"/>
+    <hyperlink ref="A90" r:id="rId87" xr:uid="{128B0657-F79E-4B56-8104-5CCA33A435AC}"/>
+    <hyperlink ref="A92" r:id="rId88" xr:uid="{441F6EB6-AF38-4BB0-9BF0-41BDB5CBD05F}"/>
+    <hyperlink ref="A93" r:id="rId89" xr:uid="{8A4E9F84-0EEB-4A1E-AAE4-B9AE9B8F0052}"/>
+    <hyperlink ref="A95" r:id="rId90" xr:uid="{11B2EF2A-E9B2-4EF7-AF75-C14C63FD9E89}"/>
+    <hyperlink ref="A97" r:id="rId91" xr:uid="{28E86E8F-E802-4F05-94FF-7B9443C6AE95}"/>
+    <hyperlink ref="A99" r:id="rId92" xr:uid="{ED5E86F0-E815-4B15-BCBF-732EF1F4A7AA}"/>
+    <hyperlink ref="A101" r:id="rId93" xr:uid="{5DEC4809-90B3-4931-B29D-012768CF29C6}"/>
+    <hyperlink ref="A103" r:id="rId94" xr:uid="{B2D5A59D-2B35-4A61-B00F-6A1F64F993CA}"/>
+    <hyperlink ref="A81" r:id="rId95" xr:uid="{E1EB28AB-505A-44C3-B632-5E1BFFE9C9E8}"/>
+    <hyperlink ref="A85" r:id="rId96" xr:uid="{A8191CE0-03D1-4706-BFA9-ED3E05A32007}"/>
+    <hyperlink ref="A87" r:id="rId97" xr:uid="{85A93914-956C-4283-8814-489D765D38DE}"/>
+    <hyperlink ref="A91" r:id="rId98" xr:uid="{3A91727D-270B-49D0-A48E-D1FF82BB6788}"/>
+    <hyperlink ref="A94" r:id="rId99" xr:uid="{A4F67A61-45DB-4F0E-A5A3-CD5B3AEBA46C}"/>
+    <hyperlink ref="A96" r:id="rId100" xr:uid="{504D8610-51E7-4D07-9221-A7AED97B4DB5}"/>
+    <hyperlink ref="A98" r:id="rId101" xr:uid="{AB84607C-8E2E-4678-BB19-04DCDACC22F2}"/>
+    <hyperlink ref="A100" r:id="rId102" xr:uid="{FEDA9EE0-AF8A-4900-9985-C6BEBFD8647C}"/>
+    <hyperlink ref="A102" r:id="rId103" xr:uid="{E3110D64-7A0C-475C-A0FF-83CAE03AEC79}"/>
+    <hyperlink ref="A104" r:id="rId104" xr:uid="{3277B967-0EA1-4030-AC2D-9914DED5C464}"/>
+    <hyperlink ref="A105" r:id="rId105" xr:uid="{E7F3C3B5-1BD7-42D7-8365-CFCEAD054FA6}"/>
+    <hyperlink ref="A106" r:id="rId106" xr:uid="{A816725E-6CC9-4B71-B7B2-DC30384A7158}"/>
+    <hyperlink ref="A107" r:id="rId107" xr:uid="{3BB8A133-3568-459C-B1D7-C1D5506EA3BC}"/>
+    <hyperlink ref="A108" r:id="rId108" xr:uid="{8077CFC9-20DA-4D22-892A-85940726193A}"/>
+    <hyperlink ref="A109" r:id="rId109" xr:uid="{E84C9FE0-A29D-4EB3-AF56-7FB9DC8741A3}"/>
+    <hyperlink ref="A110" r:id="rId110" xr:uid="{7BCF0F16-6027-487B-8B17-D625BEF38E0F}"/>
+    <hyperlink ref="A111" r:id="rId111" xr:uid="{3D0F069C-CFCC-4705-9513-8B4DE94F31D4}"/>
+    <hyperlink ref="A112" r:id="rId112" xr:uid="{C53FFF33-ED75-4C69-8F96-9CCA9AAF2659}"/>
+    <hyperlink ref="A113" r:id="rId113" xr:uid="{64702AA2-5765-4BB2-9053-EB9864AAA69B}"/>
+    <hyperlink ref="A114" r:id="rId114" xr:uid="{B829416F-6BD5-456C-89AA-EFAA40607355}"/>
+    <hyperlink ref="A115" r:id="rId115" xr:uid="{BF70B4E8-8D4F-422A-B623-23E1F258A388}"/>
+    <hyperlink ref="A116" r:id="rId116" xr:uid="{D90200C2-95EF-4DAC-AE50-C4D743304C2D}"/>
+    <hyperlink ref="A117" r:id="rId117" xr:uid="{1B1B292E-EA01-4111-A5F4-10A143B328FF}"/>
+    <hyperlink ref="A118" r:id="rId118" xr:uid="{A6B194DB-9F86-406D-9DB6-1D7A0B34E5C7}"/>
+    <hyperlink ref="A119" r:id="rId119" xr:uid="{8C6C6C41-5CED-46BB-ADF7-AE1AC14BAA6B}"/>
+    <hyperlink ref="A120" r:id="rId120" xr:uid="{B217E244-FB36-4A2F-AAE3-111B07E2C814}"/>
+    <hyperlink ref="A121" r:id="rId121" xr:uid="{265F9655-5777-4E4E-8228-478737C962AF}"/>
+    <hyperlink ref="A122" r:id="rId122" xr:uid="{28530943-609D-4B2A-BA08-A2DDDCDFAA8C}"/>
+    <hyperlink ref="A123" r:id="rId123" xr:uid="{EB9B15E3-3B35-4029-B74A-757AE54E1C63}"/>
+    <hyperlink ref="I2" r:id="rId124" xr:uid="{65EC2D52-53C6-42A9-8421-560FDFA4DFC9}"/>
+    <hyperlink ref="I3" r:id="rId125" xr:uid="{091C5530-5E9D-47E3-AE87-73F6BAEB2AB7}"/>
+    <hyperlink ref="I4" r:id="rId126" xr:uid="{B1EE5D14-1FAE-43FE-A7E8-468B7CEAEEE1}"/>
+    <hyperlink ref="I5" r:id="rId127" xr:uid="{F24CEE77-E52F-44F8-9F9A-70097ABB8AAE}"/>
+    <hyperlink ref="I7" r:id="rId128" xr:uid="{A50AF382-16AA-4D95-A888-E3B7FF9B31BB}"/>
+    <hyperlink ref="I8" r:id="rId129" xr:uid="{7DE773FC-915E-4A4C-BC49-82198A23DD68}"/>
+    <hyperlink ref="I9" r:id="rId130" xr:uid="{A099EB07-96D1-4ECD-9FCA-3D23F63AAEE1}"/>
+    <hyperlink ref="I10" r:id="rId131" xr:uid="{97DCBA74-44BC-40B2-BC4A-5472AC315E37}"/>
+    <hyperlink ref="I11" r:id="rId132" xr:uid="{D0C637A7-58CC-4A41-82EE-A9E3DD3CD2E7}"/>
+    <hyperlink ref="I12" r:id="rId133" xr:uid="{1E4B600C-7F52-4429-AA5A-C7ABBE59108D}"/>
+    <hyperlink ref="I13" r:id="rId134" xr:uid="{5A0A7DC8-3DF2-47A6-9D7D-83171563D9E8}"/>
+    <hyperlink ref="I15" r:id="rId135" xr:uid="{17FA6BB5-BEA0-4C33-A035-FCD4F27C74ED}"/>
+    <hyperlink ref="I16" r:id="rId136" xr:uid="{92B75900-B955-4EEE-B70E-0DAF3B5A1E5D}"/>
+    <hyperlink ref="I17" r:id="rId137" xr:uid="{86420AC0-7065-4E6F-B983-7FDAEBF7EE6C}"/>
+    <hyperlink ref="I19" r:id="rId138" xr:uid="{66B6CA17-A6A7-45C4-BB2F-9B5DCEC4C2EC}"/>
+    <hyperlink ref="I20" r:id="rId139" xr:uid="{338022F4-FC80-4A7A-9D90-FAF1630FA4EC}"/>
+    <hyperlink ref="I22" r:id="rId140" xr:uid="{E0815066-6CFC-493E-9C80-91135076E123}"/>
+    <hyperlink ref="I23" r:id="rId141" xr:uid="{5DF1780C-84ED-4134-87B7-6F735F5470C9}"/>
+    <hyperlink ref="I24" r:id="rId142" xr:uid="{1913AE23-D782-450F-9E12-491BE07C0E67}"/>
+    <hyperlink ref="I26" r:id="rId143" xr:uid="{AC7793A6-CE67-41C4-B65D-40683D03BF15}"/>
+    <hyperlink ref="I28" r:id="rId144" xr:uid="{C6AA0568-0789-41D6-929C-729BFF08A742}"/>
+    <hyperlink ref="I30" r:id="rId145" xr:uid="{007F13F2-A264-42D2-87C2-4F36F1381BD9}"/>
+    <hyperlink ref="I32" r:id="rId146" xr:uid="{B5F4D555-CDA2-4BD5-80DE-9F8B35AB0847}"/>
+    <hyperlink ref="I34" r:id="rId147" xr:uid="{A8E217F3-1360-4AD1-98A5-F329640BA9D1}"/>
+    <hyperlink ref="I36" r:id="rId148" xr:uid="{61A22C3D-B651-4C15-8D43-93D7469FE0EF}"/>
+    <hyperlink ref="I38" r:id="rId149" xr:uid="{E6998D78-B876-4028-8A78-1EDE006F14A5}"/>
+    <hyperlink ref="I40" r:id="rId150" xr:uid="{BE5E8B87-7A34-45E2-8F50-CD6B7B4AEDB2}"/>
+    <hyperlink ref="I42" r:id="rId151" xr:uid="{46E271FF-91B3-4EFD-809E-A38FC09D082B}"/>
+    <hyperlink ref="I14" r:id="rId152" xr:uid="{B208B065-E4A8-4C78-9C09-84295C332260}"/>
+    <hyperlink ref="I18" r:id="rId153" xr:uid="{141D16C3-15EB-4697-A85F-B8FF1409CC3D}"/>
+    <hyperlink ref="I21" r:id="rId154" xr:uid="{F60F9902-BE3D-43D4-BA06-29CC8E19F217}"/>
+    <hyperlink ref="I25" r:id="rId155" xr:uid="{0DD45575-042D-4526-B397-CE9FA9E10EC7}"/>
+    <hyperlink ref="I27" r:id="rId156" xr:uid="{BF877CEB-670E-4E76-87CA-5FEAB10414FF}"/>
+    <hyperlink ref="I29" r:id="rId157" xr:uid="{EB955D86-E626-40DC-9070-F5DF3A17E82F}"/>
+    <hyperlink ref="I31" r:id="rId158" xr:uid="{9AC74380-1A33-4C36-B19D-82F69FEF9C72}"/>
+    <hyperlink ref="I33" r:id="rId159" xr:uid="{7CBB4EC1-C023-4283-9E09-F4D745EDE798}"/>
+    <hyperlink ref="I35" r:id="rId160" xr:uid="{B705AB8E-BDD4-4816-A227-84A107EDA016}"/>
+    <hyperlink ref="I37" r:id="rId161" xr:uid="{D9BFAB2A-C725-4C2B-8689-943D4700128B}"/>
+    <hyperlink ref="I39" r:id="rId162" xr:uid="{9E16E67C-93B2-4B9E-A64A-5BA7D0768AAD}"/>
+    <hyperlink ref="I41" r:id="rId163" xr:uid="{793AA19A-DFF4-4733-9A4E-136F93EA7D33}"/>
+    <hyperlink ref="I43" r:id="rId164" xr:uid="{20FE18C5-FE7E-4E5F-85FE-36049DC2361D}"/>
+    <hyperlink ref="I44" r:id="rId165" xr:uid="{23853E74-F686-475F-B24F-255B19CDE730}"/>
+    <hyperlink ref="I45" r:id="rId166" xr:uid="{329962DC-1B11-4E1F-90BB-2FAA5FF09B61}"/>
+    <hyperlink ref="I46" r:id="rId167" xr:uid="{4305FC93-AA17-4502-987A-18E04B42E433}"/>
+    <hyperlink ref="I47" r:id="rId168" xr:uid="{25A13969-64DE-4E7C-87E2-30ED69BA7965}"/>
+    <hyperlink ref="I48" r:id="rId169" xr:uid="{D9EBD548-99DF-4D69-B387-4D45E975D93F}"/>
+    <hyperlink ref="I49" r:id="rId170" xr:uid="{F1758B8B-3AC4-4C01-9124-0D15960AC465}"/>
+    <hyperlink ref="I50" r:id="rId171" xr:uid="{7681DE31-7ADE-40AA-AB80-2AE78C08A2FA}"/>
+    <hyperlink ref="I51" r:id="rId172" xr:uid="{21E52DF8-9B4A-484C-9CF1-0D5831AF7385}"/>
+    <hyperlink ref="I52" r:id="rId173" xr:uid="{73D9B00C-D57E-4CE7-B41A-7968FE384849}"/>
+    <hyperlink ref="I53" r:id="rId174" xr:uid="{65233CF4-31B9-440A-B654-C071774BD582}"/>
+    <hyperlink ref="I54" r:id="rId175" xr:uid="{431A63F5-6EA5-4BF5-8B55-FED18BBD9223}"/>
+    <hyperlink ref="I55" r:id="rId176" xr:uid="{A6329E5E-16FE-4D22-B66C-79058FAC24C6}"/>
+    <hyperlink ref="I56" r:id="rId177" xr:uid="{37C9772F-035B-452A-9E66-BB69779F1499}"/>
+    <hyperlink ref="I57" r:id="rId178" xr:uid="{3815174D-8F00-40EE-A96B-B4CA9F503546}"/>
+    <hyperlink ref="I58" r:id="rId179" xr:uid="{49029301-6676-4703-BA5D-7A4FAFD6778D}"/>
+    <hyperlink ref="I59" r:id="rId180" xr:uid="{A4A1BC76-EA2A-4D8F-8F13-F32F450C87F7}"/>
+    <hyperlink ref="I60" r:id="rId181" xr:uid="{FDC5A507-F63F-48D8-B032-96DA9C62371F}"/>
+    <hyperlink ref="I61" r:id="rId182" xr:uid="{5BDEE148-F1E2-44B8-B5F9-E5B3DB52B9B3}"/>
+    <hyperlink ref="I62" r:id="rId183" xr:uid="{D3C18327-0489-479B-AB0B-1621BFAA97BC}"/>
+    <hyperlink ref="I63" r:id="rId184" xr:uid="{E4A429D9-372D-447A-94D0-F465CAEEDB1E}"/>
+    <hyperlink ref="I64" r:id="rId185" xr:uid="{02F746E6-1EFA-4708-8AB8-1554DD949C97}"/>
+    <hyperlink ref="I65" r:id="rId186" xr:uid="{D10BFBA3-D580-401F-825C-1A457F8E518D}"/>
+    <hyperlink ref="I66" r:id="rId187" xr:uid="{DCF9B681-5874-4FA7-82FF-D49EC2F5CD91}"/>
+    <hyperlink ref="I67" r:id="rId188" xr:uid="{E5C7A414-4B79-415A-B0DC-62F46941D60D}"/>
+    <hyperlink ref="I68" r:id="rId189" xr:uid="{843F3CDA-CD77-42AD-9BA5-43ED9E675AB0}"/>
+    <hyperlink ref="I69" r:id="rId190" xr:uid="{CBC7A1DF-3A43-46FE-A065-C165B5DF3530}"/>
+    <hyperlink ref="I70" r:id="rId191" xr:uid="{71A74632-719F-4325-947C-163ACE6DEB99}"/>
+    <hyperlink ref="I71" r:id="rId192" xr:uid="{42E4C840-6A75-4E6D-B59D-83C988C88A8E}"/>
+    <hyperlink ref="I72" r:id="rId193" xr:uid="{565DCC8B-4506-4DEE-8B41-8739A49EB6CE}"/>
+    <hyperlink ref="I73" r:id="rId194" xr:uid="{FE1ACF88-85CA-4563-93EE-82D42BC3132F}"/>
+    <hyperlink ref="I74" r:id="rId195" xr:uid="{B3F8B9ED-79B9-487E-8200-DAB86484F404}"/>
+    <hyperlink ref="I75" r:id="rId196" xr:uid="{106A597F-A18C-4448-A8F2-940452E252C4}"/>
+    <hyperlink ref="I77" r:id="rId197" xr:uid="{D93431DA-C505-4727-8160-C819CB628C57}"/>
+    <hyperlink ref="I78" r:id="rId198" xr:uid="{050BA67F-E1A8-4542-8A2F-390C2C6176A1}"/>
+    <hyperlink ref="I79" r:id="rId199" xr:uid="{125CEFD3-22B8-4FF6-8B95-0E73FC6CB209}"/>
+    <hyperlink ref="I81" r:id="rId200" xr:uid="{62333DF2-D9A3-4295-AD4D-F9823D49BCE4}"/>
+    <hyperlink ref="I82" r:id="rId201" xr:uid="{0ECCB9DE-C4F1-4EEB-A6EB-51E1A1BF4395}"/>
+    <hyperlink ref="I84" r:id="rId202" xr:uid="{60FC1F69-A0A4-4AC9-A494-86055EE19995}"/>
+    <hyperlink ref="I85" r:id="rId203" xr:uid="{187CB084-2025-44BD-A34F-E9BE2F3FCEA8}"/>
+    <hyperlink ref="I83" r:id="rId204" xr:uid="{F871C94C-F26E-4F7E-9399-745360BF9EF2}"/>
+    <hyperlink ref="I80" r:id="rId205" xr:uid="{4864A617-9AA6-4F9B-B57D-5C9E16E5C5C1}"/>
+    <hyperlink ref="I86" r:id="rId206" xr:uid="{0F971F6F-9934-420D-9C67-74D77A8853B8}"/>
+    <hyperlink ref="I87" r:id="rId207" xr:uid="{A87ECD34-F9AE-46EE-B4FA-32CD1623EF7D}"/>
+    <hyperlink ref="I88" r:id="rId208" xr:uid="{3F7367A3-9CDB-4435-8909-05E17A5656D4}"/>
+    <hyperlink ref="I89" r:id="rId209" xr:uid="{B6E75043-0BB9-4B29-9D77-4C8602012152}"/>
+    <hyperlink ref="I90" r:id="rId210" xr:uid="{715487D9-A5C9-45CD-8826-0101C380639F}"/>
+    <hyperlink ref="I91" r:id="rId211" xr:uid="{5D924EC0-07CC-4B51-A919-935EF47BD22B}"/>
+    <hyperlink ref="I92" r:id="rId212" xr:uid="{2137D6D0-EC09-4E62-90AB-C123B07F0DA5}"/>
+    <hyperlink ref="I93" r:id="rId213" xr:uid="{C60533AC-CB50-4BBB-B9BC-36609523A496}"/>
+    <hyperlink ref="I94" r:id="rId214" xr:uid="{0A129F72-EC6C-4FFB-AB7C-2B69C1AADCB5}"/>
+    <hyperlink ref="I95" r:id="rId215" xr:uid="{E11C2DB9-F212-44DF-B98B-A016D63B3CC0}"/>
+    <hyperlink ref="I97" r:id="rId216" xr:uid="{88B47E7D-44B7-4235-8280-B232216D5669}"/>
+    <hyperlink ref="I99" r:id="rId217" xr:uid="{80127CE4-F0B6-40B4-BFF3-3E4A758FBD1D}"/>
+    <hyperlink ref="I100" r:id="rId218" xr:uid="{B2D81F40-2805-45C1-962A-11A785C858EC}"/>
+    <hyperlink ref="I102" r:id="rId219" xr:uid="{2EF5D040-DF81-46AD-A893-9540E759176E}"/>
+    <hyperlink ref="I104" r:id="rId220" xr:uid="{0EE28E60-4727-4CAF-8DCB-DC1406A5BAE4}"/>
+    <hyperlink ref="I105" r:id="rId221" xr:uid="{DE57D007-D1FB-4428-8DFB-63087AE738FD}"/>
+    <hyperlink ref="I106" r:id="rId222" xr:uid="{E010F612-EC07-4F9A-B93D-CA4B78F45676}"/>
+    <hyperlink ref="I107" r:id="rId223" xr:uid="{3959A935-CCCA-442B-BC16-CFD554D98EF1}"/>
+    <hyperlink ref="I108" r:id="rId224" xr:uid="{05F3437E-CDE6-4C4A-BA25-E34E0B73AD53}"/>
+    <hyperlink ref="I110" r:id="rId225" xr:uid="{5A201480-4432-493F-82B3-113B8B68DB44}"/>
+    <hyperlink ref="I111" r:id="rId226" xr:uid="{82D905BF-CF0D-4EFD-AE12-F88920776B29}"/>
+    <hyperlink ref="I109" r:id="rId227" xr:uid="{808DFEDA-1551-43D3-A6E7-AA3E7067C649}"/>
+    <hyperlink ref="I112" r:id="rId228" xr:uid="{42AF6C0E-DA7F-46F7-A85A-0D99EB7F385F}"/>
+    <hyperlink ref="I113" r:id="rId229" xr:uid="{80D73843-EBB2-4E08-97DD-B451DE2142DF}"/>
+    <hyperlink ref="I114" r:id="rId230" xr:uid="{AD580094-7792-497F-B5AC-3C3ED0BF11CD}"/>
+    <hyperlink ref="I115" r:id="rId231" xr:uid="{9B0E21F8-4735-4AB5-93E5-ED5E98A1F536}"/>
+    <hyperlink ref="I116" r:id="rId232" xr:uid="{05794D3A-8E7C-4BC2-A041-BCAF27552179}"/>
+    <hyperlink ref="I117" r:id="rId233" xr:uid="{1B76CE97-D852-4422-AF2B-E712A895A3E3}"/>
+    <hyperlink ref="I118" r:id="rId234" xr:uid="{381DD8D5-DD11-46C5-AB0B-24628811D10F}"/>
+    <hyperlink ref="I120" r:id="rId235" xr:uid="{D0F512EE-6A29-4CF4-B66E-1F40D31E4414}"/>
+    <hyperlink ref="I119" r:id="rId236" xr:uid="{8CFD0349-CC7C-4630-A682-F5D79E0CD058}"/>
+    <hyperlink ref="I121" r:id="rId237" xr:uid="{2CBFB2C6-3832-439E-99E9-95253AB5CAB7}"/>
+    <hyperlink ref="I123" r:id="rId238" xr:uid="{1F94F81F-FBAA-493D-8ED8-97FDEB66F306}"/>
+    <hyperlink ref="I122" r:id="rId239" xr:uid="{595CB660-6C01-40E0-AAF6-5CC533774BF0}"/>
+    <hyperlink ref="I103" r:id="rId240" xr:uid="{5C2FCA29-A577-4ABB-90AF-EF59B8C759C7}"/>
+    <hyperlink ref="I101" r:id="rId241" xr:uid="{C17A0FA3-3A2B-47C1-8445-E5CE088EC202}"/>
+    <hyperlink ref="I98" r:id="rId242" xr:uid="{6AAAEC91-E180-467D-A6B7-A39CA6DFB015}"/>
+    <hyperlink ref="I96" r:id="rId243" xr:uid="{FA4EBF70-F004-4D13-BCF4-EEDB388A9D59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
